--- a/data/trans_orig/PROV-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/PROV-Provincia-trans_orig.xlsx
@@ -8901,12 +8901,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>695723</t>
+          <t>694886</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>790642</t>
+          <t>792285</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>737809</t>
+          <t>734827</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>834720</t>
+          <t>833875</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1451735</t>
+          <t>1459036</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>1593708</t>
+          <t>1595420</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>572067</t>
+          <t>567409</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>664365</t>
+          <t>657103</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9029,12 +9029,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>588043</t>
+          <t>595710</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>682118</t>
+          <t>681621</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1185271</t>
+          <t>1186868</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>1314596</t>
+          <t>1319893</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -9127,12 +9127,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>237214</t>
+          <t>240229</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>302786</t>
+          <t>301773</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>248331</t>
+          <t>247631</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>311992</t>
+          <t>310281</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>505220</t>
+          <t>505798</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>595216</t>
+          <t>593694</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>176573</t>
+          <t>178823</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>230992</t>
+          <t>231248</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>180963</t>
+          <t>179399</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>236839</t>
+          <t>235089</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>373527</t>
+          <t>372544</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>452973</t>
+          <t>452069</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>323465</t>
+          <t>325885</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>397838</t>
+          <t>395822</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>340287</t>
+          <t>339502</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>411292</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>681532</t>
+          <t>678861</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>782088</t>
+          <t>784544</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>284734</t>
+          <t>287158</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>353900</t>
+          <t>354039</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>301461</t>
+          <t>303528</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>366737</t>
+          <t>373070</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>608768</t>
+          <t>604620</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>704341</t>
+          <t>701540</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -9579,12 +9579,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>457013</t>
+          <t>451459</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>538108</t>
+          <t>539809</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>461532</t>
+          <t>462844</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>545817</t>
+          <t>543270</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>938960</t>
+          <t>939320</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>1052273</t>
+          <t>1056730</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>244188</t>
+          <t>245427</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>306148</t>
+          <t>306746</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>232974</t>
+          <t>233463</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>294138</t>
+          <t>295449</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>490206</t>
+          <t>495343</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>583708</t>
+          <t>583578</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -18326,12 +18326,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>730609</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>831125</t>
+          <t>827349</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -18341,12 +18341,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -18361,12 +18361,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>769118</t>
+          <t>769035</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>873039</t>
+          <t>870971</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1530661</t>
+          <t>1531038</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>1677776</t>
+          <t>1677506</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -18439,12 +18439,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>616373</t>
+          <t>613242</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>712708</t>
+          <t>713381</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -18454,12 +18454,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -18474,12 +18474,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>648412</t>
+          <t>646853</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>742887</t>
+          <t>742263</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -18489,12 +18489,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1283825</t>
+          <t>1287330</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>1418075</t>
+          <t>1428482</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -18524,12 +18524,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -18552,12 +18552,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>244600</t>
+          <t>241188</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>309821</t>
+          <t>307251</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -18567,12 +18567,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>248372</t>
+          <t>250180</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>316239</t>
+          <t>315222</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -18622,12 +18622,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>502996</t>
+          <t>508155</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>599058</t>
+          <t>599862</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -18637,12 +18637,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -18665,12 +18665,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>186163</t>
+          <t>183696</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>242501</t>
+          <t>239680</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -18680,12 +18680,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -18700,12 +18700,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>192638</t>
+          <t>189865</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>249801</t>
+          <t>249193</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -18715,12 +18715,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>394120</t>
+          <t>393387</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>477762</t>
+          <t>474826</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -18750,12 +18750,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -18778,12 +18778,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>333307</t>
+          <t>341831</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>409098</t>
+          <t>415278</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -18793,12 +18793,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -18813,12 +18813,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>355647</t>
+          <t>353353</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>425414</t>
+          <t>429647</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -18828,12 +18828,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -18848,12 +18848,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>708412</t>
+          <t>713920</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>817041</t>
+          <t>819308</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -18863,12 +18863,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -18891,12 +18891,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>289498</t>
+          <t>291713</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>359287</t>
+          <t>356787</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -18906,12 +18906,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>308661</t>
+          <t>306199</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>376757</t>
+          <t>378608</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -18941,12 +18941,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>614976</t>
+          <t>612127</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>715710</t>
+          <t>713565</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -19004,12 +19004,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>466490</t>
+          <t>459139</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>551841</t>
+          <t>545637</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -19019,12 +19019,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -19039,12 +19039,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>482896</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>571098</t>
+          <t>571072</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -19074,12 +19074,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>970725</t>
+          <t>968262</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>1088729</t>
+          <t>1100832</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -19117,12 +19117,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>265587</t>
+          <t>259726</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>335018</t>
+          <t>331331</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -19132,12 +19132,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -19152,12 +19152,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>253685</t>
+          <t>253881</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>322469</t>
+          <t>320977</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -19187,12 +19187,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>537422</t>
+          <t>533447</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>634102</t>
+          <t>634772</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -27751,12 +27751,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>732255</t>
+          <t>731261</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>832880</t>
+          <t>825716</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -27766,12 +27766,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -27786,12 +27786,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>774060</t>
+          <t>774135</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>872669</t>
+          <t>877183</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1535201</t>
+          <t>1537373</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>1678494</t>
+          <t>1677370</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -27836,12 +27836,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -27864,12 +27864,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>609660</t>
+          <t>608499</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>706371</t>
+          <t>704937</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -27899,12 +27899,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>648800</t>
+          <t>642809</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>742661</t>
+          <t>736915</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -27914,12 +27914,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1281488</t>
+          <t>1279870</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>1413622</t>
+          <t>1413719</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -27977,12 +27977,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>231833</t>
+          <t>232645</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>294725</t>
+          <t>294659</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -27992,47 +27992,47 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>273115</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>242108</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>309311</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>273115</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>240655</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>305280</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -28047,12 +28047,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>492206</t>
+          <t>494230</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>585276</t>
+          <t>580776</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -28062,12 +28062,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -28090,12 +28090,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>185738</t>
+          <t>185893</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>239682</t>
+          <t>241657</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -28105,12 +28105,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -28125,12 +28125,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>188177</t>
+          <t>192361</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>248847</t>
+          <t>246476</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -28140,12 +28140,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -28160,12 +28160,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>389773</t>
+          <t>389193</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>469414</t>
+          <t>470847</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -28175,12 +28175,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -28203,12 +28203,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>335345</t>
+          <t>336567</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>410173</t>
+          <t>406396</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -28218,49 +28218,49 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>387283</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>350793</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>428022</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>387283</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>350644</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>426064</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>712</t>
@@ -28273,12 +28273,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>708771</t>
+          <t>703562</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>812606</t>
+          <t>812739</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -28316,12 +28316,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>286846</t>
+          <t>288110</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>355069</t>
+          <t>350239</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -28331,49 +28331,49 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>336309</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>301611</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>370608</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>336309</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>302632</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>373989</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>667</t>
@@ -28386,12 +28386,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>607254</t>
+          <t>602738</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>704585</t>
+          <t>701035</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -28401,12 +28401,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -28429,12 +28429,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>454512</t>
+          <t>464245</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>543103</t>
+          <t>544108</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -28444,12 +28444,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -28464,12 +28464,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>480772</t>
+          <t>480999</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>563377</t>
+          <t>571490</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -28499,12 +28499,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>970326</t>
+          <t>965973</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>1086717</t>
+          <t>1090032</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -28514,12 +28514,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -28542,12 +28542,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>262747</t>
+          <t>259827</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>329170</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -28557,12 +28557,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -28577,12 +28577,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>257930</t>
+          <t>258709</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>320472</t>
+          <t>324708</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -28592,12 +28592,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -28612,12 +28612,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>535862</t>
+          <t>536599</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>633386</t>
+          <t>633651</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -29794,7 +29794,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -29907,17 +29907,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -29942,17 +29942,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -29977,17 +29977,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -30928,17 +30928,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -30963,17 +30963,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -30998,17 +30998,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -31645,7 +31645,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -31949,17 +31949,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -31984,17 +31984,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -32019,17 +32019,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -32553,7 +32553,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -32588,7 +32588,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -32970,17 +32970,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -33005,17 +33005,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -33040,17 +33040,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -33461,7 +33461,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -33496,7 +33496,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -33991,17 +33991,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -34026,17 +34026,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -34061,17 +34061,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -35012,17 +35012,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -35047,17 +35047,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -35082,17 +35082,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -35242,7 +35242,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -35277,7 +35277,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -36033,17 +36033,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -36068,17 +36068,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -36103,17 +36103,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -36220,7 +36220,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -37054,17 +37054,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -37089,17 +37089,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -37124,17 +37124,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -37171,32 +37171,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>722909</t>
+          <t>745142</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1484965</t>
+          <t>856815</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -37206,32 +37206,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>586540</t>
+          <t>786847</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>786837</t>
+          <t>875245</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -37241,32 +37241,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1407903</t>
+          <t>1560385</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2281782</t>
+          <t>1698182</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -37284,32 +37284,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>495215</t>
+          <t>665620</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>698902</t>
+          <t>784366</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -37319,32 +37319,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>669858</t>
+          <t>726065</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>1403124</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -37354,32 +37354,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1264482</t>
+          <t>1417664</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>1998385</t>
+          <t>1561534</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -37397,32 +37397,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>206319</t>
+          <t>244154</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>305167</t>
+          <t>300659</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -37432,32 +37432,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>210108</t>
+          <t>238590</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>290455</t>
+          <t>288744</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -37467,32 +37467,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>452548</t>
+          <t>499225</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>577545</t>
+          <t>572734</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -37510,32 +37510,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>138309</t>
+          <t>180840</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>203225</t>
+          <t>230815</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -37545,32 +37545,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>199197</t>
+          <t>208258</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>449091</t>
+          <t>252859</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -37580,32 +37580,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>370921</t>
+          <t>402007</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>624555</t>
+          <t>466283</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -37623,32 +37623,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>249788</t>
+          <t>328811</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>362443</t>
+          <t>426600</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -37658,32 +37658,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>375092</t>
+          <t>384895</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>693322</t>
+          <t>460237</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -37693,32 +37693,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>670922</t>
+          <t>735887</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>856193</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -37736,32 +37736,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>249221</t>
+          <t>282687</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>357125</t>
+          <t>349618</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -37771,32 +37771,32 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>279109</t>
+          <t>329230</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>388135</t>
+          <t>389121</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -37806,32 +37806,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>585100</t>
+          <t>629697</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>730478</t>
+          <t>716727</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -37849,32 +37849,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>404073</t>
+          <t>483489</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>587224</t>
+          <t>584075</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -37884,32 +37884,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>418202</t>
+          <t>507619</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>568510</t>
+          <t>583279</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -37919,32 +37919,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>878806</t>
+          <t>1013089</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>1121095</t>
+          <t>1142010</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -37962,32 +37962,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>242054</t>
+          <t>287026</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>360450</t>
+          <t>356450</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -37997,32 +37997,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>238417</t>
+          <t>288655</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>323479</t>
+          <t>346982</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -38032,32 +38032,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>519770</t>
+          <t>587945</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>666668</t>
+          <t>680103</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -38075,17 +38075,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -38110,17 +38110,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -38145,17 +38145,17 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
